--- a/servers/maze_main_server_dev/conf.d/data/maze_initial_attr_v8【迷宫-角色初始化属性】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_initial_attr_v8【迷宫-角色初始化属性】.xlsx
@@ -8,18 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659DB3BF-C170-4B3C-A662-9343F3810A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D644E7C8-CBC4-4EBC-9216-C924ADF7E84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0D60895A-DDB0-4BC5-B867-EBFA7264D275}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0D60895A-DDB0-4BC5-B867-EBFA7264D275}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_initial_attr_v8" sheetId="1" r:id="rId1"/>
     <sheet name="备注" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -94,7 +103,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3041201:200_3041301:20000_3000101:200_3041401:0_3010101:5_3020101:2_3030101:150</t>
+    <t>3041201:200_3041301:20000_3000101:200_3041401:0_3010101:100_3020101:20_3030101:3000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server_dev/conf.d/data/maze_initial_attr_v8【迷宫-角色初始化属性】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_initial_attr_v8【迷宫-角色初始化属性】.xlsx
@@ -8,27 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D644E7C8-CBC4-4EBC-9216-C924ADF7E84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659DB3BF-C170-4B3C-A662-9343F3810A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0D60895A-DDB0-4BC5-B867-EBFA7264D275}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0D60895A-DDB0-4BC5-B867-EBFA7264D275}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_initial_attr_v8" sheetId="1" r:id="rId1"/>
     <sheet name="备注" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -103,7 +94,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3041201:200_3041301:20000_3000101:200_3041401:0_3010101:100_3020101:20_3030101:3000</t>
+    <t>3041201:200_3041301:20000_3000101:200_3041401:0_3010101:5_3020101:2_3030101:150</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server_dev/conf.d/data/maze_initial_attr_v8【迷宫-角色初始化属性】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_initial_attr_v8【迷宫-角色初始化属性】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659DB3BF-C170-4B3C-A662-9343F3810A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B688E883-247B-45E1-857E-4F88A41127AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0D60895A-DDB0-4BC5-B867-EBFA7264D275}"/>
   </bookViews>
@@ -16,10 +16,19 @@
     <sheet name="maze_initial_attr_v8" sheetId="1" r:id="rId1"/>
     <sheet name="备注" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -94,7 +103,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3041201:200_3041301:20000_3000101:200_3041401:0_3010101:5_3020101:2_3030101:150</t>
+    <t>3041301:20000_3000101:200_3041401:0_3010101:10_3020101:2_3030101:160_9101:40</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
